--- a/output/output/breakpoint_estimates_aic.xlsx
+++ b/output/output/breakpoint_estimates_aic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="662">
   <si>
     <t xml:space="preserve">species</t>
   </si>
@@ -353,6 +353,18 @@
     <t xml:space="preserve">3382</t>
   </si>
   <si>
+    <t xml:space="preserve">3.714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31</t>
+  </si>
+  <si>
     <t xml:space="preserve">842</t>
   </si>
   <si>
@@ -485,6 +497,18 @@
     <t xml:space="preserve">4220</t>
   </si>
   <si>
+    <t xml:space="preserve">3.125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168</t>
+  </si>
+  <si>
     <t xml:space="preserve">1736</t>
   </si>
   <si>
@@ -632,6 +656,18 @@
     <t xml:space="preserve">big skate</t>
   </si>
   <si>
+    <t xml:space="preserve">9.354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756</t>
+  </si>
+  <si>
     <t xml:space="preserve">388</t>
   </si>
   <si>
@@ -641,6 +677,18 @@
     <t xml:space="preserve">8</t>
   </si>
   <si>
+    <t xml:space="preserve">6.766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531</t>
+  </si>
+  <si>
     <t xml:space="preserve">264</t>
   </si>
   <si>
@@ -864,6 +912,18 @@
   </si>
   <si>
     <t xml:space="preserve">spotted ratfish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.075</t>
   </si>
   <si>
     <t xml:space="preserve">4876</t>
@@ -3232,19 +3292,19 @@
         <v>19</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="K21" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="L21" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="M21" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="N21" t="s">
         <v>21</v>
@@ -3291,7 +3351,7 @@
         <v>18</v>
       </c>
       <c r="M22" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="N22" t="s">
         <v>44</v>
@@ -3302,7 +3362,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
@@ -3311,7 +3371,7 @@
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -3320,10 +3380,10 @@
         <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H23" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
@@ -3338,7 +3398,7 @@
         <v>18</v>
       </c>
       <c r="M23" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N23" t="s">
         <v>21</v>
@@ -3349,7 +3409,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -3364,13 +3424,13 @@
         <v>18</v>
       </c>
       <c r="F24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G24" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I24" t="s">
         <v>18</v>
@@ -3385,7 +3445,7 @@
         <v>18</v>
       </c>
       <c r="M24" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N24" t="s">
         <v>21</v>
@@ -3396,7 +3456,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -3405,19 +3465,19 @@
         <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F25" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G25" t="s">
         <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I25" t="s">
         <v>18</v>
@@ -3432,7 +3492,7 @@
         <v>18</v>
       </c>
       <c r="M25" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="N25" t="s">
         <v>44</v>
@@ -3443,19 +3503,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
         <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -3479,39 +3539,39 @@
         <v>18</v>
       </c>
       <c r="M26" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N26" t="s">
         <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B27" t="s">
         <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
         <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
       </c>
       <c r="G27" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H27" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
@@ -3526,54 +3586,54 @@
         <v>18</v>
       </c>
       <c r="M27" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N27" t="s">
         <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E28" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F28" t="s">
         <v>19</v>
       </c>
       <c r="G28" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J28" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K28" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="M28" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="N28" t="s">
         <v>21</v>
@@ -3584,28 +3644,28 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H29" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I29" t="s">
         <v>18</v>
@@ -3620,18 +3680,18 @@
         <v>18</v>
       </c>
       <c r="M29" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="N29" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O29" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
@@ -3640,19 +3700,19 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G30" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H30" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I30" t="s">
         <v>18</v>
@@ -3667,7 +3727,7 @@
         <v>18</v>
       </c>
       <c r="M30" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="N30" t="s">
         <v>21</v>
@@ -3678,7 +3738,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B31" t="s">
         <v>23</v>
@@ -3702,19 +3762,19 @@
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="K31" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="L31" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="M31" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="N31" t="s">
         <v>21</v>
@@ -3725,10 +3785,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B32" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
@@ -3761,7 +3821,7 @@
         <v>18</v>
       </c>
       <c r="M32" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="N32" t="s">
         <v>21</v>
@@ -3772,7 +3832,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
@@ -3808,10 +3868,10 @@
         <v>18</v>
       </c>
       <c r="M33" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="N33" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O33" t="s">
         <v>52</v>
@@ -3819,7 +3879,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B34" t="s">
         <v>16</v>
@@ -3831,16 +3891,16 @@
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
       </c>
       <c r="G34" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H34" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I34" t="s">
         <v>18</v>
@@ -3855,7 +3915,7 @@
         <v>18</v>
       </c>
       <c r="M34" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="N34" t="s">
         <v>21</v>
@@ -3866,7 +3926,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B35" t="s">
         <v>23</v>
@@ -3902,7 +3962,7 @@
         <v>18</v>
       </c>
       <c r="M35" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="N35" t="s">
         <v>21</v>
@@ -3913,7 +3973,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
@@ -3922,7 +3982,7 @@
         <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E36" t="s">
         <v>18</v>
@@ -3949,7 +4009,7 @@
         <v>18</v>
       </c>
       <c r="M36" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="N36" t="s">
         <v>44</v>
@@ -3960,7 +4020,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
@@ -3978,7 +4038,7 @@
         <v>18</v>
       </c>
       <c r="G37" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
@@ -3996,7 +4056,7 @@
         <v>18</v>
       </c>
       <c r="M37" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="N37" t="s">
         <v>21</v>
@@ -4007,7 +4067,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B38" t="s">
         <v>23</v>
@@ -4043,7 +4103,7 @@
         <v>18</v>
       </c>
       <c r="M38" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="N38" t="s">
         <v>21</v>
@@ -4054,10 +4114,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
@@ -4066,16 +4126,16 @@
         <v>19</v>
       </c>
       <c r="E39" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F39" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G39" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H39" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I39" t="s">
         <v>18</v>
@@ -4090,7 +4150,7 @@
         <v>18</v>
       </c>
       <c r="M39" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N39" t="s">
         <v>21</v>
@@ -4101,7 +4161,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B40" t="s">
         <v>34</v>
@@ -4110,16 +4170,16 @@
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E40" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F40" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G40" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H40" t="s">
         <v>19</v>
@@ -4137,10 +4197,10 @@
         <v>18</v>
       </c>
       <c r="M40" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="N40" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O40" t="s">
         <v>52</v>
@@ -4148,7 +4208,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s">
         <v>16</v>
@@ -4157,19 +4217,19 @@
         <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G41" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H41" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I41" t="s">
         <v>18</v>
@@ -4184,7 +4244,7 @@
         <v>18</v>
       </c>
       <c r="M41" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="N41" t="s">
         <v>21</v>
@@ -4195,7 +4255,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B42" t="s">
         <v>23</v>
@@ -4231,7 +4291,7 @@
         <v>18</v>
       </c>
       <c r="M42" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="N42" t="s">
         <v>21</v>
@@ -4242,7 +4302,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B43" t="s">
         <v>34</v>
@@ -4251,16 +4311,16 @@
         <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="E43" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
       </c>
       <c r="G43" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="H43" t="s">
         <v>19</v>
@@ -4278,7 +4338,7 @@
         <v>18</v>
       </c>
       <c r="M43" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="N43" t="s">
         <v>44</v>
@@ -4289,7 +4349,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B44" t="s">
         <v>16</v>
@@ -4325,7 +4385,7 @@
         <v>18</v>
       </c>
       <c r="M44" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="N44" t="s">
         <v>21</v>
@@ -4336,7 +4396,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B45" t="s">
         <v>23</v>
@@ -4357,7 +4417,7 @@
         <v>18</v>
       </c>
       <c r="H45" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I45" t="s">
         <v>18</v>
@@ -4372,7 +4432,7 @@
         <v>18</v>
       </c>
       <c r="M45" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="N45" t="s">
         <v>21</v>
@@ -4383,10 +4443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
@@ -4404,22 +4464,22 @@
         <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I46" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="J46" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="K46" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="L46" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="M46" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="N46" t="s">
         <v>21</v>
@@ -4430,7 +4490,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B47" t="s">
         <v>34</v>
@@ -4442,13 +4502,13 @@
         <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="F47" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G47" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="H47" t="s">
         <v>19</v>
@@ -4466,10 +4526,10 @@
         <v>18</v>
       </c>
       <c r="M47" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N47" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O47" t="s">
         <v>45</v>
@@ -4477,7 +4537,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s">
         <v>23</v>
@@ -4501,19 +4561,19 @@
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>18</v>
+        <v>214</v>
       </c>
       <c r="J48" t="s">
-        <v>18</v>
+        <v>215</v>
       </c>
       <c r="K48" t="s">
-        <v>18</v>
+        <v>216</v>
       </c>
       <c r="L48" t="s">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="M48" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="N48" t="s">
         <v>21</v>
@@ -4524,10 +4584,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B49" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
@@ -4571,7 +4631,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s">
         <v>34</v>
@@ -4607,24 +4667,24 @@
         <v>18</v>
       </c>
       <c r="M50" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="N50" t="s">
         <v>44</v>
       </c>
       <c r="O50" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -4642,36 +4702,36 @@
         <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>18</v>
+        <v>221</v>
       </c>
       <c r="J51" t="s">
-        <v>18</v>
+        <v>222</v>
       </c>
       <c r="K51" t="s">
-        <v>18</v>
+        <v>223</v>
       </c>
       <c r="L51" t="s">
-        <v>18</v>
+        <v>224</v>
       </c>
       <c r="M51" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="N51" t="s">
         <v>21</v>
       </c>
       <c r="O51" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B52" t="s">
         <v>23</v>
       </c>
       <c r="C52" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D52" t="s">
         <v>19</v>
@@ -4701,24 +4761,24 @@
         <v>18</v>
       </c>
       <c r="M52" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="N52" t="s">
         <v>21</v>
       </c>
       <c r="O52" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -4748,7 +4808,7 @@
         <v>18</v>
       </c>
       <c r="M53" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="N53" t="s">
         <v>21</v>
@@ -4759,13 +4819,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B54" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C54" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -4795,33 +4855,33 @@
         <v>18</v>
       </c>
       <c r="M54" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="N54" t="s">
         <v>21</v>
       </c>
       <c r="O54" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B55" t="s">
         <v>34</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D55" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="E55" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="F55" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="G55" t="s">
         <v>18</v>
@@ -4830,30 +4890,30 @@
         <v>19</v>
       </c>
       <c r="I55" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="J55" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="K55" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="L55" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="M55" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="N55" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O55" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="B56" t="s">
         <v>16</v>
@@ -4862,19 +4922,19 @@
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="E56" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="F56" t="s">
         <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="H56" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="I56" t="s">
         <v>18</v>
@@ -4889,7 +4949,7 @@
         <v>18</v>
       </c>
       <c r="M56" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="N56" t="s">
         <v>21</v>
@@ -4900,7 +4960,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="B57" t="s">
         <v>23</v>
@@ -4909,7 +4969,7 @@
         <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
@@ -4936,7 +4996,7 @@
         <v>18</v>
       </c>
       <c r="M57" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="N57" t="s">
         <v>21</v>
@@ -4947,7 +5007,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="B58" t="s">
         <v>34</v>
@@ -4956,19 +5016,19 @@
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="E58" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="F58" t="s">
         <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="H58" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="I58" t="s">
         <v>18</v>
@@ -4983,7 +5043,7 @@
         <v>18</v>
       </c>
       <c r="M58" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="N58" t="s">
         <v>44</v>
@@ -4994,7 +5054,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B59" t="s">
         <v>16</v>
@@ -5012,7 +5072,7 @@
         <v>18</v>
       </c>
       <c r="G59" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
@@ -5030,7 +5090,7 @@
         <v>18</v>
       </c>
       <c r="M59" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="N59" t="s">
         <v>21</v>
@@ -5041,7 +5101,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B60" t="s">
         <v>23</v>
@@ -5050,34 +5110,34 @@
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="E60" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="F60" t="s">
         <v>18</v>
       </c>
       <c r="G60" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="H60" t="s">
         <v>19</v>
       </c>
       <c r="I60" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="J60" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="K60" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="L60" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="M60" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="N60" t="s">
         <v>21</v>
@@ -5088,7 +5148,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B61" t="s">
         <v>34</v>
@@ -5097,13 +5157,13 @@
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="G61" t="s">
         <v>18</v>
@@ -5124,7 +5184,7 @@
         <v>18</v>
       </c>
       <c r="M61" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="N61" t="s">
         <v>44</v>
@@ -5135,7 +5195,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="B62" t="s">
         <v>16</v>
@@ -5144,16 +5204,16 @@
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="E62" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="F62" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="G62" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="H62" t="s">
         <v>19</v>
@@ -5171,7 +5231,7 @@
         <v>18</v>
       </c>
       <c r="M62" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="N62" t="s">
         <v>21</v>
@@ -5182,7 +5242,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="B63" t="s">
         <v>23</v>
@@ -5191,16 +5251,16 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="E63" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="F63" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="G63" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="H63" t="s">
         <v>19</v>
@@ -5218,7 +5278,7 @@
         <v>18</v>
       </c>
       <c r="M63" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="N63" t="s">
         <v>21</v>
@@ -5229,28 +5289,28 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="B64" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="E64" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="F64" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="G64" t="s">
         <v>19</v>
       </c>
       <c r="H64" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="I64" t="s">
         <v>18</v>
@@ -5265,7 +5325,7 @@
         <v>18</v>
       </c>
       <c r="M64" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="N64" t="s">
         <v>21</v>
@@ -5276,10 +5336,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="B65" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
@@ -5294,7 +5354,7 @@
         <v>18</v>
       </c>
       <c r="G65" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="H65" t="s">
         <v>19</v>
@@ -5312,7 +5372,7 @@
         <v>18</v>
       </c>
       <c r="M65" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="N65" t="s">
         <v>21</v>
@@ -5323,7 +5383,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="B66" t="s">
         <v>34</v>
@@ -5332,19 +5392,19 @@
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="E66" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="F66" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="G66" t="s">
         <v>19</v>
       </c>
       <c r="H66" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="I66" t="s">
         <v>18</v>
@@ -5359,18 +5419,18 @@
         <v>18</v>
       </c>
       <c r="M66" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="N66" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O66" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B67" t="s">
         <v>16</v>
@@ -5406,7 +5466,7 @@
         <v>18</v>
       </c>
       <c r="M67" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="N67" t="s">
         <v>21</v>
@@ -5417,7 +5477,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B68" t="s">
         <v>23</v>
@@ -5453,7 +5513,7 @@
         <v>18</v>
       </c>
       <c r="M68" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="N68" t="s">
         <v>21</v>
@@ -5464,10 +5524,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C69" t="s">
         <v>17</v>
@@ -5485,7 +5545,7 @@
         <v>18</v>
       </c>
       <c r="H69" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="I69" t="s">
         <v>18</v>
@@ -5500,7 +5560,7 @@
         <v>18</v>
       </c>
       <c r="M69" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="N69" t="s">
         <v>21</v>
@@ -5511,7 +5571,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B70" t="s">
         <v>34</v>
@@ -5523,7 +5583,7 @@
         <v>19</v>
       </c>
       <c r="E70" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="F70" t="s">
         <v>18</v>
@@ -5547,10 +5607,10 @@
         <v>18</v>
       </c>
       <c r="M70" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="N70" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O70" t="s">
         <v>45</v>
@@ -5558,13 +5618,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B71" t="s">
         <v>16</v>
       </c>
       <c r="C71" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -5594,24 +5654,24 @@
         <v>18</v>
       </c>
       <c r="M71" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="N71" t="s">
         <v>21</v>
       </c>
       <c r="O71" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B72" t="s">
         <v>23</v>
       </c>
       <c r="C72" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -5641,24 +5701,24 @@
         <v>18</v>
       </c>
       <c r="M72" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="N72" t="s">
         <v>21</v>
       </c>
       <c r="O72" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -5688,7 +5748,7 @@
         <v>18</v>
       </c>
       <c r="M73" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="N73" t="s">
         <v>21</v>
@@ -5699,16 +5759,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B74" t="s">
         <v>34</v>
       </c>
       <c r="C74" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D74" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="E74" t="s">
         <v>18</v>
@@ -5735,18 +5795,18 @@
         <v>18</v>
       </c>
       <c r="M74" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="N74" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O74" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B75" t="s">
         <v>16</v>
@@ -5770,19 +5830,19 @@
         <v>19</v>
       </c>
       <c r="I75" t="s">
-        <v>18</v>
+        <v>300</v>
       </c>
       <c r="J75" t="s">
-        <v>18</v>
+        <v>301</v>
       </c>
       <c r="K75" t="s">
-        <v>18</v>
+        <v>302</v>
       </c>
       <c r="L75" t="s">
-        <v>18</v>
+        <v>303</v>
       </c>
       <c r="M75" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="N75" t="s">
         <v>21</v>
@@ -5793,7 +5853,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B76" t="s">
         <v>23</v>
@@ -5802,34 +5862,34 @@
         <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="E76" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="F76" t="s">
         <v>19</v>
       </c>
       <c r="G76" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="H76" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="I76" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="J76" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="K76" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="L76" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="M76" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="N76" t="s">
         <v>21</v>
@@ -5840,7 +5900,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B77" t="s">
         <v>34</v>
@@ -5849,34 +5909,34 @@
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="E77" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="F77" t="s">
         <v>19</v>
       </c>
       <c r="G77" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="J77" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="K77" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="L77" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="M77" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="N77" t="s">
         <v>44</v>
@@ -5887,7 +5947,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B78" t="s">
         <v>16</v>
@@ -5896,19 +5956,19 @@
         <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G78" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="H78" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="I78" t="s">
         <v>18</v>
@@ -5923,7 +5983,7 @@
         <v>18</v>
       </c>
       <c r="M78" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="N78" t="s">
         <v>21</v>
@@ -5934,7 +5994,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B79" t="s">
         <v>23</v>
@@ -5943,13 +6003,13 @@
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="E79" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="F79" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="G79" t="s">
         <v>19</v>
@@ -5970,7 +6030,7 @@
         <v>18</v>
       </c>
       <c r="M79" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="N79" t="s">
         <v>21</v>
@@ -5981,10 +6041,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B80" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C80" t="s">
         <v>17</v>
@@ -6017,7 +6077,7 @@
         <v>18</v>
       </c>
       <c r="M80" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="N80" t="s">
         <v>21</v>
@@ -6028,16 +6088,16 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B81" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C81" t="s">
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="E81" t="s">
         <v>18</v>
@@ -6049,7 +6109,7 @@
         <v>19</v>
       </c>
       <c r="H81" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="I81" t="s">
         <v>18</v>
@@ -6064,7 +6124,7 @@
         <v>18</v>
       </c>
       <c r="M81" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="N81" t="s">
         <v>21</v>
@@ -6075,7 +6135,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B82" t="s">
         <v>34</v>
@@ -6084,16 +6144,16 @@
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="E82" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F82" t="s">
         <v>19</v>
       </c>
       <c r="G82" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
@@ -6111,10 +6171,10 @@
         <v>18</v>
       </c>
       <c r="M82" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="N82" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O82" t="s">
         <v>52</v>
@@ -6122,7 +6182,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="B83" t="s">
         <v>16</v>
@@ -6134,7 +6194,7 @@
         <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="F83" t="s">
         <v>18</v>
@@ -6158,7 +6218,7 @@
         <v>18</v>
       </c>
       <c r="M83" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="N83" t="s">
         <v>21</v>
@@ -6169,7 +6229,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="B84" t="s">
         <v>23</v>
@@ -6181,16 +6241,16 @@
         <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="F84" t="s">
         <v>19</v>
       </c>
       <c r="G84" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="H84" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="I84" t="s">
         <v>18</v>
@@ -6205,7 +6265,7 @@
         <v>18</v>
       </c>
       <c r="M84" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="N84" t="s">
         <v>21</v>
@@ -6216,7 +6276,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="B85" t="s">
         <v>34</v>
@@ -6225,7 +6285,7 @@
         <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="E85" t="s">
         <v>19</v>
@@ -6252,7 +6312,7 @@
         <v>18</v>
       </c>
       <c r="M85" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="N85" t="s">
         <v>44</v>
@@ -6263,7 +6323,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="B86" t="s">
         <v>16</v>
@@ -6272,10 +6332,10 @@
         <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="E86" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="F86" t="s">
         <v>18</v>
@@ -6287,19 +6347,19 @@
         <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="J86" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="K86" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="L86" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="M86" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="N86" t="s">
         <v>21</v>
@@ -6310,7 +6370,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="B87" t="s">
         <v>23</v>
@@ -6319,13 +6379,13 @@
         <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="E87" t="s">
         <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="G87" t="s">
         <v>18</v>
@@ -6346,7 +6406,7 @@
         <v>18</v>
       </c>
       <c r="M87" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="N87" t="s">
         <v>21</v>
@@ -6357,10 +6417,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="B88" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C88" t="s">
         <v>17</v>
@@ -6369,16 +6429,16 @@
         <v>19</v>
       </c>
       <c r="E88" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="F88" t="s">
         <v>18</v>
       </c>
       <c r="G88" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="H88" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="I88" t="s">
         <v>18</v>
@@ -6393,7 +6453,7 @@
         <v>18</v>
       </c>
       <c r="M88" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="N88" t="s">
         <v>21</v>
@@ -6404,28 +6464,28 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="B89" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C89" t="s">
         <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="E89" t="s">
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="G89" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="H89" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="I89" t="s">
         <v>18</v>
@@ -6440,7 +6500,7 @@
         <v>18</v>
       </c>
       <c r="M89" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="N89" t="s">
         <v>21</v>
@@ -6451,7 +6511,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="B90" t="s">
         <v>34</v>
@@ -6469,7 +6529,7 @@
         <v>19</v>
       </c>
       <c r="G90" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
@@ -6487,10 +6547,10 @@
         <v>18</v>
       </c>
       <c r="M90" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="N90" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O90" t="s">
         <v>52</v>
@@ -6498,7 +6558,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="B91" t="s">
         <v>16</v>
@@ -6534,7 +6594,7 @@
         <v>18</v>
       </c>
       <c r="M91" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="N91" t="s">
         <v>21</v>
@@ -6545,7 +6605,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="B92" t="s">
         <v>23</v>
@@ -6554,7 +6614,7 @@
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="E92" t="s">
         <v>18</v>
@@ -6566,7 +6626,7 @@
         <v>19</v>
       </c>
       <c r="H92" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="I92" t="s">
         <v>18</v>
@@ -6581,7 +6641,7 @@
         <v>18</v>
       </c>
       <c r="M92" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="N92" t="s">
         <v>21</v>
@@ -6592,7 +6652,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="B93" t="s">
         <v>34</v>
@@ -6601,19 +6661,19 @@
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="E93" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="F93" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="G93" t="s">
         <v>19</v>
       </c>
       <c r="H93" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="I93" t="s">
         <v>18</v>
@@ -6628,7 +6688,7 @@
         <v>18</v>
       </c>
       <c r="M93" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="N93" t="s">
         <v>44</v>
@@ -6639,16 +6699,16 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="B94" t="s">
         <v>16</v>
       </c>
       <c r="C94" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D94" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="E94" t="s">
         <v>19</v>
@@ -6675,7 +6735,7 @@
         <v>18</v>
       </c>
       <c r="M94" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="N94" t="s">
         <v>21</v>
@@ -6686,28 +6746,28 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="B95" t="s">
         <v>23</v>
       </c>
       <c r="C95" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D95" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="E95" t="s">
         <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="G95" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H95" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="I95" t="s">
         <v>18</v>
@@ -6722,30 +6782,30 @@
         <v>18</v>
       </c>
       <c r="M95" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="N95" t="s">
         <v>21</v>
       </c>
       <c r="O95" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="B96" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C96" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D96" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="E96" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="F96" t="s">
         <v>19</v>
@@ -6757,19 +6817,19 @@
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="J96" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="K96" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="L96" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="M96" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="N96" t="s">
         <v>21</v>
@@ -6780,16 +6840,16 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="B97" t="s">
         <v>34</v>
       </c>
       <c r="C97" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D97" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="E97" t="s">
         <v>19</v>
@@ -6816,18 +6876,18 @@
         <v>18</v>
       </c>
       <c r="M97" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="N97" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O97" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B98" t="s">
         <v>16</v>
@@ -6863,7 +6923,7 @@
         <v>18</v>
       </c>
       <c r="M98" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="N98" t="s">
         <v>21</v>
@@ -6874,7 +6934,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B99" t="s">
         <v>23</v>
@@ -6883,34 +6943,34 @@
         <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="E99" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="F99" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="G99" t="s">
         <v>19</v>
       </c>
       <c r="H99" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="I99" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="J99" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="K99" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="L99" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="M99" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="N99" t="s">
         <v>21</v>
@@ -6921,10 +6981,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B100" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C100" t="s">
         <v>17</v>
@@ -6957,7 +7017,7 @@
         <v>18</v>
       </c>
       <c r="M100" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="N100" t="s">
         <v>21</v>
@@ -6968,43 +7028,43 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B101" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C101" t="s">
         <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="E101" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="F101" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="G101" t="s">
         <v>19</v>
       </c>
       <c r="H101" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="I101" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="J101" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="K101" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="L101" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="M101" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="N101" t="s">
         <v>21</v>
@@ -7015,7 +7075,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B102" t="s">
         <v>34</v>
@@ -7024,37 +7084,37 @@
         <v>17</v>
       </c>
       <c r="D102" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E102" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="F102" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="G102" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="H102" t="s">
         <v>19</v>
       </c>
       <c r="I102" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="J102" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="K102" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="L102" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="M102" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="N102" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O102" t="s">
         <v>52</v>
@@ -7062,90 +7122,90 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B103" t="s">
         <v>16</v>
       </c>
       <c r="C103" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D103" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="E103" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="F103" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="G103" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="H103" t="s">
         <v>19</v>
       </c>
       <c r="I103" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="J103" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="K103" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L103" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="M103" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="N103" t="s">
         <v>21</v>
       </c>
       <c r="O103" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B104" t="s">
         <v>23</v>
       </c>
       <c r="C104" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D104" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E104" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="F104" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="G104" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="H104" t="s">
         <v>19</v>
       </c>
       <c r="I104" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="J104" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="K104" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="L104" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="M104" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="N104" t="s">
         <v>21</v>
@@ -7156,148 +7216,148 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B105" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C105" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D105" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="E105" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="F105" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="G105" t="s">
         <v>19</v>
       </c>
       <c r="H105" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="I105" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="J105" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="K105" t="s">
         <v>78</v>
       </c>
       <c r="L105" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="M105" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="N105" t="s">
         <v>21</v>
       </c>
       <c r="O105" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B106" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C106" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D106" t="s">
         <v>18</v>
       </c>
       <c r="E106" t="s">
+        <v>450</v>
+      </c>
+      <c r="F106" t="s">
+        <v>451</v>
+      </c>
+      <c r="G106" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" t="s">
+        <v>452</v>
+      </c>
+      <c r="I106" t="s">
+        <v>453</v>
+      </c>
+      <c r="J106" t="s">
+        <v>454</v>
+      </c>
+      <c r="K106" t="s">
         <v>430</v>
       </c>
-      <c r="F106" t="s">
-        <v>431</v>
-      </c>
-      <c r="G106" t="s">
-        <v>19</v>
-      </c>
-      <c r="H106" t="s">
-        <v>432</v>
-      </c>
-      <c r="I106" t="s">
-        <v>433</v>
-      </c>
-      <c r="J106" t="s">
-        <v>434</v>
-      </c>
-      <c r="K106" t="s">
-        <v>410</v>
-      </c>
       <c r="L106" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="M106" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="N106" t="s">
         <v>21</v>
       </c>
       <c r="O106" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B107" t="s">
         <v>34</v>
       </c>
       <c r="C107" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D107" t="s">
         <v>18</v>
       </c>
       <c r="E107" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="F107" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="G107" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="H107" t="s">
         <v>19</v>
       </c>
       <c r="I107" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="J107" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="K107" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="L107" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="M107" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="N107" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O107" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B108" t="s">
         <v>16</v>
@@ -7306,19 +7366,19 @@
         <v>17</v>
       </c>
       <c r="D108" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="E108" t="s">
         <v>19</v>
       </c>
       <c r="F108" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G108" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="H108" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="I108" t="s">
         <v>18</v>
@@ -7333,7 +7393,7 @@
         <v>18</v>
       </c>
       <c r="M108" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="N108" t="s">
         <v>21</v>
@@ -7344,7 +7404,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B109" t="s">
         <v>23</v>
@@ -7353,13 +7413,13 @@
         <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E109" t="s">
         <v>19</v>
       </c>
       <c r="F109" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G109" t="s">
         <v>18</v>
@@ -7380,7 +7440,7 @@
         <v>18</v>
       </c>
       <c r="M109" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="N109" t="s">
         <v>21</v>
@@ -7391,10 +7451,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B110" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C110" t="s">
         <v>17</v>
@@ -7427,7 +7487,7 @@
         <v>18</v>
       </c>
       <c r="M110" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="N110" t="s">
         <v>21</v>
@@ -7438,7 +7498,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B111" t="s">
         <v>34</v>
@@ -7459,7 +7519,7 @@
         <v>18</v>
       </c>
       <c r="H111" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="I111" t="s">
         <v>18</v>
@@ -7474,10 +7534,10 @@
         <v>18</v>
       </c>
       <c r="M111" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="N111" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O111" t="s">
         <v>45</v>
@@ -7485,22 +7545,22 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B112" t="s">
         <v>16</v>
       </c>
       <c r="C112" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D112" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="E112" t="s">
         <v>19</v>
       </c>
       <c r="F112" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="G112" t="s">
         <v>18</v>
@@ -7521,80 +7581,80 @@
         <v>18</v>
       </c>
       <c r="M112" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="N112" t="s">
         <v>21</v>
       </c>
       <c r="O112" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B113" t="s">
         <v>23</v>
       </c>
       <c r="C113" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D113" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="E113" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="F113" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="G113" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="H113" t="s">
         <v>19</v>
       </c>
       <c r="I113" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="J113" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="K113" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="L113" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="M113" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="N113" t="s">
         <v>21</v>
       </c>
       <c r="O113" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B114" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C114" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D114" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="E114" t="s">
         <v>18</v>
       </c>
       <c r="F114" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="G114" t="s">
         <v>19</v>
@@ -7603,19 +7663,19 @@
         <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="J114" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="K114" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="L114" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="M114" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="N114" t="s">
         <v>21</v>
@@ -7626,25 +7686,25 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B115" t="s">
         <v>34</v>
       </c>
       <c r="C115" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D115" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="E115" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="F115" t="s">
         <v>19</v>
       </c>
       <c r="G115" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
@@ -7662,18 +7722,18 @@
         <v>18</v>
       </c>
       <c r="M115" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="N115" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O115" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B116" t="s">
         <v>16</v>
@@ -7682,10 +7742,10 @@
         <v>17</v>
       </c>
       <c r="D116" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="E116" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="F116" t="s">
         <v>18</v>
@@ -7697,19 +7757,19 @@
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="J116" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="K116" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="L116" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="M116" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="N116" t="s">
         <v>21</v>
@@ -7720,7 +7780,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B117" t="s">
         <v>23</v>
@@ -7738,7 +7798,7 @@
         <v>18</v>
       </c>
       <c r="G117" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="H117" t="s">
         <v>19</v>
@@ -7756,7 +7816,7 @@
         <v>18</v>
       </c>
       <c r="M117" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="N117" t="s">
         <v>21</v>
@@ -7767,10 +7827,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B118" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C118" t="s">
         <v>17</v>
@@ -7803,7 +7863,7 @@
         <v>18</v>
       </c>
       <c r="M118" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="N118" t="s">
         <v>21</v>
@@ -7814,28 +7874,28 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B119" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C119" t="s">
         <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="E119" t="s">
         <v>19</v>
       </c>
       <c r="F119" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G119" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H119" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I119" t="s">
         <v>18</v>
@@ -7850,7 +7910,7 @@
         <v>18</v>
       </c>
       <c r="M119" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="N119" t="s">
         <v>21</v>
@@ -7861,7 +7921,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B120" t="s">
         <v>34</v>
@@ -7870,37 +7930,37 @@
         <v>17</v>
       </c>
       <c r="D120" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="E120" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="F120" t="s">
         <v>19</v>
       </c>
       <c r="G120" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="H120" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="I120" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="J120" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="K120" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="L120" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="M120" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="N120" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O120" t="s">
         <v>52</v>
@@ -7908,19 +7968,19 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B121" t="s">
         <v>16</v>
       </c>
       <c r="C121" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D121" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="E121" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="F121" t="s">
         <v>18</v>
@@ -7932,89 +7992,89 @@
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="J121" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="K121" t="s">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="L121" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="M121" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="N121" t="s">
         <v>21</v>
       </c>
       <c r="O121" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B122" t="s">
         <v>23</v>
       </c>
       <c r="C122" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D122" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="E122" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="F122" t="s">
         <v>19</v>
       </c>
       <c r="G122" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="J122" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="K122" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="L122" t="s">
         <v>77</v>
       </c>
       <c r="M122" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="N122" t="s">
         <v>21</v>
       </c>
       <c r="O122" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B123" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C123" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D123" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="E123" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="F123" t="s">
         <v>18</v>
@@ -8023,22 +8083,22 @@
         <v>19</v>
       </c>
       <c r="H123" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="I123" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="J123" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="K123" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="L123" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="M123" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="N123" t="s">
         <v>21</v>
@@ -8049,25 +8109,25 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C124" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D124" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="E124" t="s">
         <v>18</v>
       </c>
       <c r="F124" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="G124" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="H124" t="s">
         <v>19</v>
@@ -8085,65 +8145,65 @@
         <v>18</v>
       </c>
       <c r="M124" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="N124" t="s">
         <v>21</v>
       </c>
       <c r="O124" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B125" t="s">
         <v>34</v>
       </c>
       <c r="C125" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D125" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="E125" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F125" t="s">
         <v>19</v>
       </c>
       <c r="G125" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="H125" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="I125" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="J125" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="K125" t="s">
         <v>86</v>
       </c>
       <c r="L125" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="M125" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="N125" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O125" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="B126" t="s">
         <v>23</v>
@@ -8152,19 +8212,19 @@
         <v>17</v>
       </c>
       <c r="D126" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="E126" t="s">
         <v>19</v>
       </c>
       <c r="F126" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="G126" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H126" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="I126" t="s">
         <v>18</v>
@@ -8179,7 +8239,7 @@
         <v>18</v>
       </c>
       <c r="M126" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="N126" t="s">
         <v>21</v>
@@ -8190,16 +8250,16 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C127" t="s">
         <v>17</v>
       </c>
       <c r="D127" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="E127" t="s">
         <v>18</v>
@@ -8214,19 +8274,19 @@
         <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="J127" t="s">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="K127" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="L127" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="M127" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="N127" t="s">
         <v>21</v>
@@ -8237,10 +8297,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="B128" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C128" t="s">
         <v>17</v>
@@ -8249,7 +8309,7 @@
         <v>19</v>
       </c>
       <c r="E128" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="F128" t="s">
         <v>18</v>
@@ -8258,7 +8318,7 @@
         <v>18</v>
       </c>
       <c r="H128" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="I128" t="s">
         <v>18</v>
@@ -8273,7 +8333,7 @@
         <v>18</v>
       </c>
       <c r="M128" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="N128" t="s">
         <v>21</v>
@@ -8284,7 +8344,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="B129" t="s">
         <v>34</v>
@@ -8293,19 +8353,19 @@
         <v>17</v>
       </c>
       <c r="D129" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="E129" t="s">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="F129" t="s">
         <v>19</v>
       </c>
       <c r="G129" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="H129" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="I129" t="s">
         <v>18</v>
@@ -8320,18 +8380,18 @@
         <v>18</v>
       </c>
       <c r="M129" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="N129" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O129" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="B130" t="s">
         <v>16</v>
@@ -8340,10 +8400,10 @@
         <v>17</v>
       </c>
       <c r="D130" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="E130" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="F130" t="s">
         <v>18</v>
@@ -8355,19 +8415,19 @@
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="J130" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="K130" t="s">
-        <v>554</v>
+        <v>574</v>
       </c>
       <c r="L130" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="M130" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="N130" t="s">
         <v>21</v>
@@ -8378,7 +8438,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="B131" t="s">
         <v>23</v>
@@ -8387,16 +8447,16 @@
         <v>17</v>
       </c>
       <c r="D131" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="E131" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="F131" t="s">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="G131" t="s">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="H131" t="s">
         <v>19</v>
@@ -8414,7 +8474,7 @@
         <v>18</v>
       </c>
       <c r="M131" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="N131" t="s">
         <v>21</v>
@@ -8425,10 +8485,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="B132" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C132" t="s">
         <v>17</v>
@@ -8437,7 +8497,7 @@
         <v>19</v>
       </c>
       <c r="E132" t="s">
-        <v>561</v>
+        <v>581</v>
       </c>
       <c r="F132" t="s">
         <v>18</v>
@@ -8446,7 +8506,7 @@
         <v>18</v>
       </c>
       <c r="H132" t="s">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="I132" t="s">
         <v>18</v>
@@ -8461,7 +8521,7 @@
         <v>18</v>
       </c>
       <c r="M132" t="s">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="N132" t="s">
         <v>21</v>
@@ -8472,10 +8532,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="B133" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -8508,7 +8568,7 @@
         <v>18</v>
       </c>
       <c r="M133" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="N133" t="s">
         <v>21</v>
@@ -8519,7 +8579,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="B134" t="s">
         <v>34</v>
@@ -8528,19 +8588,19 @@
         <v>17</v>
       </c>
       <c r="D134" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="E134" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="F134" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="G134" t="s">
         <v>19</v>
       </c>
       <c r="H134" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="I134" t="s">
         <v>18</v>
@@ -8555,18 +8615,18 @@
         <v>18</v>
       </c>
       <c r="M134" t="s">
-        <v>569</v>
+        <v>589</v>
       </c>
       <c r="N134" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O134" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="B135" t="s">
         <v>23</v>
@@ -8602,7 +8662,7 @@
         <v>18</v>
       </c>
       <c r="M135" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="N135" t="s">
         <v>21</v>
@@ -8613,16 +8673,16 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="B136" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C136" t="s">
         <v>17</v>
       </c>
       <c r="D136" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="E136" t="s">
         <v>19</v>
@@ -8631,10 +8691,10 @@
         <v>18</v>
       </c>
       <c r="G136" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="H136" t="s">
-        <v>574</v>
+        <v>594</v>
       </c>
       <c r="I136" t="s">
         <v>18</v>
@@ -8649,7 +8709,7 @@
         <v>18</v>
       </c>
       <c r="M136" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="N136" t="s">
         <v>21</v>
@@ -8660,10 +8720,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="B137" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -8672,10 +8732,10 @@
         <v>18</v>
       </c>
       <c r="E137" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="F137" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="G137" t="s">
         <v>19</v>
@@ -8696,7 +8756,7 @@
         <v>18</v>
       </c>
       <c r="M137" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="N137" t="s">
         <v>21</v>
@@ -8707,7 +8767,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="B138" t="s">
         <v>34</v>
@@ -8716,45 +8776,45 @@
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="E138" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="F138" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="G138" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="H138" t="s">
         <v>19</v>
       </c>
       <c r="I138" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="J138" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="K138" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L138" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="M138" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="N138" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O138" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="B139" t="s">
         <v>16</v>
@@ -8790,7 +8850,7 @@
         <v>18</v>
       </c>
       <c r="M139" t="s">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="N139" t="s">
         <v>21</v>
@@ -8801,7 +8861,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="B140" t="s">
         <v>23</v>
@@ -8813,7 +8873,7 @@
         <v>18</v>
       </c>
       <c r="E140" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="F140" t="s">
         <v>18</v>
@@ -8837,7 +8897,7 @@
         <v>18</v>
       </c>
       <c r="M140" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="N140" t="s">
         <v>21</v>
@@ -8848,10 +8908,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="B141" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
@@ -8863,28 +8923,28 @@
         <v>18</v>
       </c>
       <c r="F141" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="G141" t="s">
         <v>19</v>
       </c>
       <c r="H141" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I141" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="J141" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="K141" t="s">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="L141" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
       <c r="M141" t="s">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="N141" t="s">
         <v>21</v>
@@ -8895,19 +8955,19 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="B142" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="E142" t="s">
-        <v>597</v>
+        <v>617</v>
       </c>
       <c r="F142" t="s">
         <v>18</v>
@@ -8931,7 +8991,7 @@
         <v>18</v>
       </c>
       <c r="M142" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="N142" t="s">
         <v>21</v>
@@ -8942,7 +9002,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="B143" t="s">
         <v>34</v>
@@ -8951,45 +9011,45 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="E143" t="s">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="F143" t="s">
-        <v>601</v>
+        <v>621</v>
       </c>
       <c r="G143" t="s">
         <v>19</v>
       </c>
       <c r="H143" t="s">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="I143" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="J143" t="s">
         <v>37</v>
       </c>
       <c r="K143" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="L143" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="M143" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="N143" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O143" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="B144" t="s">
         <v>16</v>
@@ -8998,7 +9058,7 @@
         <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="E144" t="s">
         <v>19</v>
@@ -9010,7 +9070,7 @@
         <v>18</v>
       </c>
       <c r="H144" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I144" t="s">
         <v>18</v>
@@ -9025,7 +9085,7 @@
         <v>18</v>
       </c>
       <c r="M144" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="N144" t="s">
         <v>21</v>
@@ -9036,7 +9096,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="B145" t="s">
         <v>23</v>
@@ -9072,7 +9132,7 @@
         <v>18</v>
       </c>
       <c r="M145" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="N145" t="s">
         <v>21</v>
@@ -9083,7 +9143,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="B146" t="s">
         <v>34</v>
@@ -9092,7 +9152,7 @@
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="E146" t="s">
         <v>19</v>
@@ -9101,10 +9161,10 @@
         <v>18</v>
       </c>
       <c r="G146" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H146" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I146" t="s">
         <v>18</v>
@@ -9119,7 +9179,7 @@
         <v>18</v>
       </c>
       <c r="M146" t="s">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="N146" t="s">
         <v>44</v>
@@ -9130,7 +9190,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B147" t="s">
         <v>16</v>
@@ -9139,16 +9199,16 @@
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="E147" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="F147" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="G147" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="H147" t="s">
         <v>19</v>
@@ -9166,7 +9226,7 @@
         <v>18</v>
       </c>
       <c r="M147" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="N147" t="s">
         <v>21</v>
@@ -9177,7 +9237,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B148" t="s">
         <v>23</v>
@@ -9192,7 +9252,7 @@
         <v>18</v>
       </c>
       <c r="F148" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="G148" t="s">
         <v>18</v>
@@ -9213,7 +9273,7 @@
         <v>18</v>
       </c>
       <c r="M148" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="N148" t="s">
         <v>21</v>
@@ -9224,16 +9284,16 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B149" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="E149" t="s">
         <v>18</v>
@@ -9260,7 +9320,7 @@
         <v>18</v>
       </c>
       <c r="M149" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="N149" t="s">
         <v>21</v>
@@ -9271,16 +9331,16 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B150" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="E150" t="s">
         <v>19</v>
@@ -9307,7 +9367,7 @@
         <v>18</v>
       </c>
       <c r="M150" t="s">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="N150" t="s">
         <v>21</v>
@@ -9318,7 +9378,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B151" t="s">
         <v>34</v>
@@ -9327,19 +9387,19 @@
         <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="E151" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="F151" t="s">
         <v>19</v>
       </c>
       <c r="G151" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="H151" t="s">
-        <v>627</v>
+        <v>647</v>
       </c>
       <c r="I151" t="s">
         <v>18</v>
@@ -9354,27 +9414,27 @@
         <v>18</v>
       </c>
       <c r="M151" t="s">
-        <v>628</v>
+        <v>648</v>
       </c>
       <c r="N151" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O151" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B152" t="s">
         <v>16</v>
       </c>
       <c r="C152" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D152" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="E152" t="s">
         <v>18</v>
@@ -9401,7 +9461,7 @@
         <v>18</v>
       </c>
       <c r="M152" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="N152" t="s">
         <v>21</v>
@@ -9412,16 +9472,16 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B153" t="s">
         <v>23</v>
       </c>
       <c r="C153" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D153" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="E153" t="s">
         <v>18</v>
@@ -9448,36 +9508,36 @@
         <v>18</v>
       </c>
       <c r="M153" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="N153" t="s">
         <v>21</v>
       </c>
       <c r="O153" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B154" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C154" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D154" t="s">
         <v>18</v>
       </c>
       <c r="E154" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="F154" t="s">
         <v>18</v>
       </c>
       <c r="G154" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="H154" t="s">
         <v>19</v>
@@ -9495,7 +9555,7 @@
         <v>18</v>
       </c>
       <c r="M154" t="s">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="N154" t="s">
         <v>21</v>
@@ -9506,13 +9566,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B155" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C155" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D155" t="s">
         <v>18</v>
@@ -9542,39 +9602,39 @@
         <v>18</v>
       </c>
       <c r="M155" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="N155" t="s">
         <v>21</v>
       </c>
       <c r="O155" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B156" t="s">
         <v>34</v>
       </c>
       <c r="C156" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D156" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="E156" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="F156" t="s">
         <v>19</v>
       </c>
       <c r="G156" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="H156" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="I156" t="s">
         <v>18</v>
@@ -9589,13 +9649,13 @@
         <v>18</v>
       </c>
       <c r="M156" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="N156" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O156" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
